--- a/data/S1991_92_FINAL.xlsx
+++ b/data/S1991_92_FINAL.xlsx
@@ -27,8 +27,11 @@
     <sheet name="SERIES" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="CLUBS" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="META" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -36,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,8 +54,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +81,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -87,12 +99,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -19899,7 +19917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19943,6 +19961,76 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1991_92_0048 'Sokol Praha -jih' prev→CLUB_S1990_91_0057 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1991_92_0429 'Brumov B' prev→CLUB_S1990_91_0505 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1991_92_0447 'Vítkovice Svinov' prev→CLUB_S1990_91_0527 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0021</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1991_92_0021 'Prolínací soutěž' (L15, parent=NODE_S1991_92_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0047</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1991_92_0047 'O postup do I.ČNHL' (L25, parent=NODE_S1991_92_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -24766,8 +24854,6 @@
         </is>
       </c>
     </row>
-    <row r="114"/>
-    <row r="115"/>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
@@ -24847,7 +24933,6 @@
         </is>
       </c>
     </row>
-    <row r="123"/>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
@@ -50778,6 +50863,171 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0048</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0048 'Sokol Praha -jih' prev→CLUB_S1990_91_0057 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0429</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0429 'Brumov B' prev→CLUB_S1990_91_0505 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0447</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0447 'Vítkovice Svinov' prev→CLUB_S1990_91_0527 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0021</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1991_92_0021 'Prolínací soutěž' (L15, parent=NODE_S1991_92_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0047</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1991_92_0047 'O postup do I.ČNHL' (L25, parent=NODE_S1991_92_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1991_92_FINAL.xlsx
+++ b/data/S1991_92_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19917,7 +19917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19967,7 +19967,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1991_92_0048 'Sokol Praha -jih' prev→CLUB_S1990_91_0057 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -19979,7 +19979,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1991_92_0429 'Brumov B' prev→CLUB_S1990_91_0505 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -19991,7 +19991,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1991_92_0447 'Vítkovice Svinov' prev→CLUB_S1990_91_0527 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -20001,14 +20001,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S1991_92_0021</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1991_92_0021 'Prolínací soutěž' (L15, parent=NODE_S1991_92_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -20018,17 +20013,408 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NODE_S1991_92_0047</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1991_92_0047 'O postup do I.ČNHL' (L25, parent=NODE_S1991_92_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK 31 Kežmarok' → 'Kežmarok' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0057 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0274 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0217 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0505 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0527 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -24854,6 +25240,8 @@
         </is>
       </c>
     </row>
+    <row r="114"/>
+    <row r="115"/>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
@@ -24884,6 +25272,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0001</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -24896,6 +25289,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0003</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -24908,6 +25306,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0003</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -24920,6 +25323,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0036</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -24933,6 +25341,7 @@
         </is>
       </c>
     </row>
+    <row r="123"/>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
@@ -26992,12 +27401,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -27034,12 +27443,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -27076,12 +27485,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slezan Opava</t>
         </is>
       </c>
     </row>
@@ -27202,12 +27611,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -27417,12 +27826,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -27637,12 +28046,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom.</t>
+          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom. || TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>SMZ Dubnica nad Váhom</t>
+          <t>Dubnica nad Váhom</t>
         </is>
       </c>
     </row>
@@ -27679,12 +28088,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -27763,12 +28172,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -28015,12 +28424,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Kežmarok = HK 31 Kežmarok (Wiki D42 - registr ustavy 04/2026). Slovensky/Prešovský kraj. **HK 31** = nova post-revolucni znacka klubu. city Kežmarok.</t>
+          <t>Kežmarok = HK 31 Kežmarok (Wiki D42 - registr ustavy 04/2026). Slovensky/Prešovský kraj. **HK 31** = nova post-revolucni znacka klubu. city Kežmarok. || TBD: city 'HK 31 Kežmarok' → 'Kežmarok' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>HK 31 Kežmarok</t>
+          <t>Kežmarok</t>
         </is>
       </c>
     </row>
@@ -28482,12 +28891,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -28744,12 +29153,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -29132,12 +29541,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -29342,12 +29751,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha.</t>
+          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha. || TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>DP I. ČLTK Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -29510,12 +29919,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov.</t>
+          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov. || TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>VVŠ PV Vyškov</t>
+          <t>Vyškov</t>
         </is>
       </c>
     </row>
@@ -29846,12 +30255,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Piešťany = HK Chirana Piešťany (Wiki D42 - registr ustavy 04/2026). Slovensky/Trnavsky kraj. city Piešťany.</t>
+          <t>Piešťany = HK Chirana Piešťany (Wiki D42 - registr ustavy 04/2026). Slovensky/Trnavsky kraj. city Piešťany. || TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>HK Chirana Piešťany</t>
+          <t>Chirana Piešťany</t>
         </is>
       </c>
     </row>
@@ -30061,12 +30470,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Nové Zámky = TJ Lokomotiva Nové Zámky (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. Železničárský klub. Patterns: Lokomotíva Nové Zámky -&gt; Lokomotiva Nové Zámky. city Nové Zámky.</t>
+          <t>Nové Zámky = TJ Lokomotiva Nové Zámky (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. Železničárský klub. Patterns: Lokomotíva Nové Zámky -&gt; Lokomotiva Nové Zámky. city Nové Zámky. || TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Lokomotiva Nové Zámky</t>
+          <t>Nové Zámky</t>
         </is>
       </c>
     </row>
@@ -34262,12 +34671,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -34435,12 +34844,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -35293,12 +35702,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -35434,12 +35843,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -36705,12 +37114,12 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu.</t>
+          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu. || TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>Start VD Luby</t>
+          <t>Luby</t>
         </is>
       </c>
     </row>
@@ -38176,12 +38585,12 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -38307,12 +38716,12 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -39132,12 +39541,12 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov.</t>
+          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov. || TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -41564,12 +41973,12 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -45896,12 +46305,12 @@
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -50869,11 +51278,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -50918,21 +51327,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0048</t>
+          <t>CLUB_S1991_92_0015</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0048 'Sokol Praha -jih' prev→CLUB_S1990_91_0057 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -50940,21 +51347,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0429</t>
+          <t>CLUB_S1991_92_0016</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0429 'Brumov B' prev→CLUB_S1990_91_0505 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -50962,21 +51367,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0447</t>
+          <t>CLUB_S1991_92_0017</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0447 'Vítkovice Svinov' prev→CLUB_S1990_91_0527 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -50984,21 +51387,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NODE_S1991_92_0021</t>
+          <t>CLUB_S1991_92_0020</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1991_92_0021 'Prolínací soutěž' (L15, parent=NODE_S1991_92_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -51006,24 +51407,682 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NODE_S1991_92_0047</t>
+          <t>CLUB_S1991_92_0025</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1991_92_0047 'O postup do I.ČNHL' (L25, parent=NODE_S1991_92_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0030</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0031</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0033</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0039</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'HK 31 Kežmarok' → 'Kežmarok' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0048</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0057 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0052</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0054</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0058</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0067</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0072</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0076</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0084</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0089</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0183</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0187</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0187</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0206</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0209</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0218</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0235</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0274 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0238</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0272</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0275</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0294</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0296</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0304</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0352</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0353</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0358</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0396</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0217 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0429</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0505 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0447</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0527 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0452</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F6"/>
+  <autoFilter ref="A1:F39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1991_92_FINAL.xlsx
+++ b/data/S1991_92_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19917,7 +19917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19967,7 +19967,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -19979,7 +19979,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -19991,7 +19991,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -20003,7 +20003,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK 31 Kežmarok' → 'Kežmarok' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -20015,7 +20015,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0057 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -20027,7 +20027,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -20039,7 +20039,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -20051,7 +20051,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -20063,7 +20063,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HK 31 Kežmarok' → 'Kežmarok' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -20075,7 +20075,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0057 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -20087,7 +20087,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -20099,7 +20099,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -20111,7 +20111,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -20123,7 +20123,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -20135,7 +20135,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -20147,7 +20147,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -20159,7 +20159,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -20171,7 +20171,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0274 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -20183,7 +20183,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -20195,7 +20195,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -20207,7 +20207,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -20219,7 +20219,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -20231,7 +20231,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -20243,7 +20243,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -20255,7 +20255,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0274 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -20267,7 +20267,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -20279,7 +20279,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -20291,7 +20291,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0217 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -20303,7 +20303,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0505 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -20315,106 +20315,10 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0527 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0217 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0505 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0527 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -20431,7 +20335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K127"/>
+  <dimension ref="A1:L127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20490,6 +20394,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20532,6 +20441,11 @@
           <t>14 týmů: 2 skupiny (Z/V) + playoff (8F/QF/SF/finále/O 3.) + o udržení. Mistr: Dukla Trenčín.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20621,6 +20535,11 @@
           <t>I.ČNHL: základ + playoff (QF/SF/finále/O 3.) + O 5.-8. + o udržení. I.SNHL (12). Kval o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20663,6 +20582,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20705,6 +20629,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20747,6 +20676,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20873,6 +20807,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0007</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -20957,6 +20896,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0008</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -20999,6 +20943,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0009</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -21041,6 +20990,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0010</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -21083,6 +21037,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0011</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -21125,6 +21084,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0012</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -21167,6 +21131,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0013</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -21209,6 +21178,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0014</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -21251,6 +21225,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0015</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -21293,6 +21272,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0016</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -21335,6 +21319,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0017</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -21377,6 +21366,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0018</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -21461,6 +21455,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0020</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -21503,6 +21502,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0021</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -21550,6 +21554,11 @@
           <t>Finálová skupina 8 týmů.</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0022</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -21592,6 +21601,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0023</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -21634,6 +21648,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0024</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -21770,6 +21789,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0029</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -21896,6 +21920,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0032</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -22022,6 +22051,11 @@
           <t>II.ČNHL: 3 skupiny + finále.</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0035</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -22064,6 +22098,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0036</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -22106,6 +22145,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0037</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -22148,6 +22192,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0038</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -22316,6 +22365,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0041</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -22358,6 +22412,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0042</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -22400,6 +22459,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0043</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -22442,6 +22506,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0044</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -22526,6 +22595,11 @@
           <t>II.SNHL 1991/92: skupina západ, střed a východ + finálová skupina + skupiny o umístění západ/střed/východ. Zdrojově neúplné: ve skupině západ chybí výsledek Levice – Topoľčany a PDF hlásí chybu ve skóre; ve skupině o umístění – střed chybějí dvě závěrečná kola.</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0046</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -22820,6 +22894,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0058</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -22862,6 +22941,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0059</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -22904,6 +22988,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0060</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -22946,6 +23035,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0061</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -23114,6 +23208,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0069</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -23156,6 +23255,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0070</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -23324,6 +23428,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0075</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -23366,6 +23475,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0076</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -23408,6 +23522,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0077</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -23450,6 +23569,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0078</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -23492,6 +23616,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0080</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -23623,6 +23752,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0083</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -23665,6 +23799,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0084</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -23707,6 +23846,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0085</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -23749,6 +23893,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0088</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -23791,6 +23940,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0089</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -24085,6 +24239,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0093</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -24127,6 +24286,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0094</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -24169,6 +24333,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0095</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -24211,6 +24380,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0096</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -24505,6 +24679,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0100</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -24547,6 +24726,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0101</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -24589,6 +24773,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0104</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -24715,6 +24904,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0102</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -24757,6 +24951,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0103</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -24799,6 +24998,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0105</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -24972,6 +25176,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0110</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -25014,6 +25223,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0111</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -25098,6 +25312,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0121</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -25145,6 +25364,11 @@
           <t>Paralelní slovenská krajská větev; v této sezóně z tohoto kraje nikdo do příští sezóny nepostoupil.</t>
         </is>
       </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0122</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -25192,6 +25416,11 @@
           <t>Paralelní slovenská krajská větev; v této sezóně z tohoto kraje nikdo do příští sezóny nepostoupil.</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0123</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -25237,6 +25466,11 @@
       <c r="K113" t="inlineStr">
         <is>
           <t>Paralelní slovenská krajská větev. Do příští sezóny postoupil z krajských přeborů TJ Baník Rožňava.</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0124</t>
         </is>
       </c>
     </row>
@@ -25260,6 +25494,11 @@
           <t>I.liga (10 týmů, jeden stůl)</t>
         </is>
       </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -25277,6 +25516,11 @@
           <t>NODE_S1991_92_0001</t>
         </is>
       </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -25294,6 +25538,11 @@
           <t>NODE_S1991_92_0003</t>
         </is>
       </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -25311,6 +25560,11 @@
           <t>NODE_S1991_92_0003</t>
         </is>
       </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -25328,6 +25582,11 @@
           <t>NODE_S1991_92_0036</t>
         </is>
       </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -25338,6 +25597,11 @@
       <c r="B122" t="inlineStr">
         <is>
           <t>Okresní přebory (jen registr)</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>okresní</t>
         </is>
       </c>
     </row>
@@ -27401,12 +27665,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -27443,12 +27707,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -27485,12 +27749,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Slezan Opava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -27826,12 +28090,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -28172,12 +28436,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -34671,12 +34935,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -34844,12 +35108,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -46305,12 +46569,12 @@
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -51278,7 +51542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -51332,12 +51596,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0015</t>
+          <t>CLUB_S1991_92_0020</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51352,12 +51616,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0016</t>
+          <t>CLUB_S1991_92_0030</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51372,12 +51636,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0017</t>
+          <t>CLUB_S1991_92_0031</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51392,12 +51656,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0020</t>
+          <t>CLUB_S1991_92_0039</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'HK 31 Kežmarok' → 'Kežmarok' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51412,12 +51676,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0025</t>
+          <t>CLUB_S1991_92_0048</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0057 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -51432,12 +51696,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0030</t>
+          <t>CLUB_S1991_92_0052</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51452,12 +51716,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0031</t>
+          <t>CLUB_S1991_92_0054</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -51472,12 +51736,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0033</t>
+          <t>CLUB_S1991_92_0058</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51492,12 +51756,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0039</t>
+          <t>CLUB_S1991_92_0067</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'HK 31 Kežmarok' → 'Kežmarok' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51512,12 +51776,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0048</t>
+          <t>CLUB_S1991_92_0072</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0057 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51532,12 +51796,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0052</t>
+          <t>CLUB_S1991_92_0076</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51552,12 +51816,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0054</t>
+          <t>CLUB_S1991_92_0084</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51572,12 +51836,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0058</t>
+          <t>CLUB_S1991_92_0089</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51592,12 +51856,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0067</t>
+          <t>CLUB_S1991_92_0187</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51612,12 +51876,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0072</t>
+          <t>CLUB_S1991_92_0206</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51632,12 +51896,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0076</t>
+          <t>CLUB_S1991_92_0209</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51652,12 +51916,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0084</t>
+          <t>CLUB_S1991_92_0218</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
     </row>
@@ -51672,12 +51936,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0089</t>
+          <t>CLUB_S1991_92_0235</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0274 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -51692,12 +51956,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0183</t>
+          <t>CLUB_S1991_92_0238</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51712,12 +51976,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0187</t>
+          <t>CLUB_S1991_92_0272</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51732,12 +51996,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0187</t>
+          <t>CLUB_S1991_92_0275</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51752,12 +52016,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0206</t>
+          <t>CLUB_S1991_92_0294</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -51772,12 +52036,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0209</t>
+          <t>CLUB_S1991_92_0296</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51792,12 +52056,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0218</t>
+          <t>CLUB_S1991_92_0304</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -51812,12 +52076,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0235</t>
+          <t>CLUB_S1991_92_0352</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0274 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -51832,12 +52096,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0238</t>
+          <t>CLUB_S1991_92_0353</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51852,12 +52116,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0272</t>
+          <t>CLUB_S1991_92_0358</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
     </row>
@@ -51872,12 +52136,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0275</t>
+          <t>CLUB_S1991_92_0396</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0217 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -51892,12 +52156,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0294</t>
+          <t>CLUB_S1991_92_0429</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0505 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -51912,177 +52176,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1991_92_0296</t>
+          <t>CLUB_S1991_92_0447</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CLUB_S1991_92_0304</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>CLUB_S1991_92_0352</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CLUB_S1991_92_0353</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>CLUB_S1991_92_0358</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>CLUB_S1991_92_0396</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0217 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>CLUB_S1991_92_0429</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0505 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CLUB_S1991_92_0447</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1990_91_0527 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>CLUB_S1991_92_0452</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F39"/>
+  <autoFilter ref="A1:F31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1991_92_FINAL.xlsx
+++ b/data/S1991_92_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19917,7 +19917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20319,6 +20319,66 @@
         </is>
       </c>
       <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -51542,7 +51602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -52185,8 +52245,108 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>HC Škoda Plzeň</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>HC Dukla Jihlava</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Poldi Kladno</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AC ZPS Zlín</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>HC Poprad</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F31"/>
+  <autoFilter ref="A1:F36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1991_92_FINAL.xlsx
+++ b/data/S1991_92_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -760,16 +760,16 @@
         <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -777,7 +777,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>139</v>
+        <v>112</v>
+      </c>
+      <c r="M5" t="n">
+        <v>49</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -838,13 +841,13 @@
         <v>19</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>166</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -852,7 +855,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>166</v>
+        <v>138</v>
+      </c>
+      <c r="M6" t="n">
+        <v>45</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -910,16 +916,16 @@
         <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -927,7 +933,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>132</v>
+        <v>97</v>
+      </c>
+      <c r="M7" t="n">
+        <v>44</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -985,16 +994,16 @@
         <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1002,7 +1011,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>134</v>
+        <v>138</v>
+      </c>
+      <c r="M8" t="n">
+        <v>42</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1063,13 +1075,13 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>146</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1077,7 +1089,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>146</v>
+        <v>127</v>
+      </c>
+      <c r="M9" t="n">
+        <v>39</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1135,16 +1150,16 @@
         <v>38</v>
       </c>
       <c r="G10" t="n">
+        <v>17</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="n">
         <v>16</v>
       </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>5</v>
-      </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1152,7 +1167,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>130</v>
+        <v>123</v>
+      </c>
+      <c r="M10" t="n">
+        <v>39</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1215,16 +1233,16 @@
         <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>113</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1232,7 +1250,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>113</v>
+        <v>169</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1327,16 +1348,16 @@
         <v>38</v>
       </c>
       <c r="G13" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>174</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1344,7 +1365,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>174</v>
+        <v>156</v>
+      </c>
+      <c r="M13" t="n">
+        <v>48</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1402,16 +1426,16 @@
         <v>38</v>
       </c>
       <c r="G14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>168</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1419,7 +1443,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>168</v>
+        <v>158</v>
+      </c>
+      <c r="M14" t="n">
+        <v>41</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1477,16 +1504,16 @@
         <v>38</v>
       </c>
       <c r="G15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>140</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1494,7 +1521,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>140</v>
+        <v>130</v>
+      </c>
+      <c r="M15" t="n">
+        <v>37</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1552,16 +1582,16 @@
         <v>38</v>
       </c>
       <c r="G16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1569,7 +1599,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>124</v>
+        <v>140</v>
+      </c>
+      <c r="M16" t="n">
+        <v>36</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1627,16 +1660,16 @@
         <v>38</v>
       </c>
       <c r="G17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>136</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1644,7 +1677,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>136</v>
+        <v>158</v>
+      </c>
+      <c r="M17" t="n">
+        <v>34</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1702,16 +1738,16 @@
         <v>38</v>
       </c>
       <c r="G18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1719,7 +1755,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>112</v>
+        <v>134</v>
+      </c>
+      <c r="M18" t="n">
+        <v>30</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1785,13 +1824,13 @@
         <v>11</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1799,7 +1838,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>118</v>
+        <v>152</v>
+      </c>
+      <c r="M19" t="n">
+        <v>28</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -19917,7 +19959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20319,66 +20361,6 @@
         </is>
       </c>
       <c r="D32" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -51602,7 +51584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -52245,108 +52227,8 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>HC Škoda Plzeň</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>HC Dukla Jihlava</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Poldi Kladno</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>AC ZPS Zlín</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>HC Poprad</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F36"/>
+  <autoFilter ref="A1:F31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1991_92_FINAL.xlsx
+++ b/data/S1991_92_FINAL.xlsx
@@ -48363,13 +48363,13 @@
         <v>26</v>
       </c>
       <c r="G8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J8" t="n">
         <v>92</v>
@@ -50778,7 +50778,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="M40" t="n">
         <v>45</v>
@@ -51238,7 +51238,7 @@
         <v>38</v>
       </c>
       <c r="J46" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -56440,7 +56440,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="M59" t="n">
         <v>7</v>

--- a/data/S1991_92_FINAL.xlsx
+++ b/data/S1991_92_FINAL.xlsx
@@ -20377,7 +20377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L127"/>
+  <dimension ref="A1:N127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20441,6 +20441,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25516,8 +25526,6 @@
         </is>
       </c>
     </row>
-    <row r="114"/>
-    <row r="115"/>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
@@ -25647,7 +25655,6 @@
         </is>
       </c>
     </row>
-    <row r="123"/>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>

--- a/data/S1991_92_FINAL.xlsx
+++ b/data/S1991_92_FINAL.xlsx
@@ -20718,6 +20718,16 @@
           <t>NODE_S1991_92_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0011</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0017</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20732,6 +20742,14 @@
         <is>
           <t>NODE_S1990_91_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -20896,6 +20914,16 @@
           <t>NODE_S1991_92_0009</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0011</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0020</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20905,6 +20933,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -20938,6 +20974,16 @@
           <t>NODE_S1991_92_0009</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0012</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0020</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20952,6 +20998,14 @@
         <is>
           <t>NODE_S1990_91_0008</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -20985,6 +21039,16 @@
           <t>NODE_S1991_92_0009</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0016</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0015</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20999,6 +21063,14 @@
         <is>
           <t>NODE_S1990_91_0009</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -21032,6 +21104,8 @@
           <t>NODE_S1991_92_0009</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21046,6 +21120,14 @@
         <is>
           <t>NODE_S1990_91_0010</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -21079,6 +21161,8 @@
           <t>NODE_S1991_92_0009</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21093,6 +21177,14 @@
         <is>
           <t>NODE_S1990_91_0011</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -21126,6 +21218,8 @@
           <t>NODE_S1991_92_0009</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21140,6 +21234,14 @@
         <is>
           <t>NODE_S1990_91_0012</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -21173,6 +21275,8 @@
           <t>NODE_S1991_92_0009</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21187,6 +21291,14 @@
         <is>
           <t>NODE_S1990_91_0013</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -21220,6 +21332,8 @@
           <t>NODE_S1991_92_0001</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21234,6 +21348,14 @@
         <is>
           <t>NODE_S1990_91_0014</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -21267,6 +21389,8 @@
           <t>NODE_S1991_92_0009</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21281,6 +21405,14 @@
         <is>
           <t>NODE_S1990_91_0015</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -21314,6 +21446,8 @@
           <t>NODE_S1991_92_0009</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21328,6 +21462,14 @@
         <is>
           <t>NODE_S1990_91_0016</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -21361,6 +21503,16 @@
           <t>NODE_S1991_92_0009</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0014</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0013</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21375,6 +21527,14 @@
         <is>
           <t>NODE_S1990_91_0017</t>
         </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -21455,6 +21615,12 @@
           <t>NODE_S1991_92_0004</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0023</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21464,6 +21630,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -21497,6 +21671,16 @@
           <t>NODE_S1991_92_0004</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0027</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21511,6 +21695,14 @@
         <is>
           <t>NODE_S1990_91_0020</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -21544,6 +21736,12 @@
           <t>NODE_S1991_92_0004</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0026</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21558,6 +21756,14 @@
         <is>
           <t>NODE_S1990_91_0021</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -21643,6 +21849,8 @@
           <t>NODE_S1991_92_0004</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21657,6 +21865,14 @@
         <is>
           <t>NODE_S1990_91_0023</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -21690,6 +21906,8 @@
           <t>NODE_S1991_92_0004</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21704,6 +21922,14 @@
         <is>
           <t>NODE_S1990_91_0024</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -21737,6 +21963,8 @@
           <t>NODE_S1991_92_0004</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21751,6 +21979,14 @@
         <is>
           <t>Skupina o 9.-14. místo. 26. kolo Opava – Hodonín 5:0 kontumačně pro nedostavení hostů. 31. kolo Karviná – HC Brno 0:5 kontumačně pro neoprávněný start hráče Karviné.</t>
         </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -21962,6 +22198,12 @@
           <t>NODE_S1991_92_0030</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0034</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21976,6 +22218,14 @@
         <is>
           <t>NODE_S1990_91_0032</t>
         </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -22009,6 +22259,8 @@
           <t>NODE_S1991_92_0030</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22018,6 +22270,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -22051,6 +22311,8 @@
           <t>NODE_S1991_92_0030</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22060,6 +22322,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -22323,6 +22593,12 @@
           <t>NODE_S1991_92_0036</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0043</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22332,6 +22608,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -22365,6 +22649,12 @@
           <t>NODE_S1991_92_0036</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0043</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22374,6 +22664,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -22407,6 +22705,8 @@
           <t>NODE_S1991_92_0036</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22421,6 +22721,14 @@
         <is>
           <t>NODE_S1990_91_0041</t>
         </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -22454,6 +22762,8 @@
           <t>NODE_S1991_92_0036</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22468,6 +22778,14 @@
         <is>
           <t>NODE_S1990_91_0042</t>
         </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -22501,6 +22819,8 @@
           <t>NODE_S1991_92_0036</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22515,6 +22835,14 @@
         <is>
           <t>NODE_S1990_91_0043</t>
         </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -22548,6 +22876,8 @@
           <t>NODE_S1991_92_0036</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22562,6 +22892,14 @@
         <is>
           <t>NODE_S1990_91_0044</t>
         </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -22810,6 +23148,8 @@
           <t>NODE_S1991_92_0049</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22819,6 +23159,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -22852,6 +23200,8 @@
           <t>NODE_S1991_92_0050</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22861,6 +23211,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -22894,6 +23252,8 @@
           <t>NODE_S1991_92_0051</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22903,6 +23263,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -22936,6 +23304,8 @@
           <t>NODE_S1991_92_0048</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22950,6 +23320,14 @@
         <is>
           <t>NODE_S1990_91_0058</t>
         </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -23077,6 +23455,16 @@
           <t>NODE_S1991_92_0058</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0061</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0062</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23091,6 +23479,14 @@
         <is>
           <t>NODE_S1990_91_0061</t>
         </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -23124,6 +23520,8 @@
           <t>NODE_S1991_92_0058</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23133,6 +23531,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -23166,6 +23572,8 @@
           <t>NODE_S1991_92_0058</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23175,6 +23583,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -23705,6 +24121,8 @@
           <t>NODE_S1991_92_0069</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23714,6 +24132,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -23747,6 +24173,8 @@
           <t>NODE_S1991_92_0069</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23756,6 +24184,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -23930,6 +24366,12 @@
           <t>REG_VYC</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0086</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23949,6 +24391,14 @@
         <is>
           <t>NODE_S1990_91_0088</t>
         </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -24239,6 +24689,8 @@
           <t>NODE_S1991_92_0079</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24248,6 +24700,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="86">
@@ -24511,6 +24971,8 @@
           <t>NODE_S1991_92_0087</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24520,6 +24982,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -24553,6 +25023,8 @@
           <t>NODE_S1991_92_0087</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24562,6 +25034,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -24595,6 +25075,8 @@
           <t>NODE_S1991_92_0087</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24604,6 +25086,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>o 11. místo</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="94">
@@ -24637,6 +25127,8 @@
           <t>NODE_S1991_92_0087</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24646,6 +25138,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="95">
@@ -24815,6 +25315,8 @@
           <t>NODE_S1991_92_0087</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24829,6 +25331,14 @@
         <is>
           <t>NODE_S1990_91_0104</t>
         </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="99">
@@ -24862,6 +25372,8 @@
           <t>NODE_S1991_92_0087</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24871,6 +25383,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -24904,6 +25424,8 @@
           <t>NODE_S1991_92_0087</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24913,6 +25435,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -25040,6 +25570,8 @@
           <t>NODE_S1991_92_0087</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25054,6 +25586,14 @@
         <is>
           <t>NODE_S1990_91_0105</t>
         </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="104">
@@ -25087,6 +25627,8 @@
           <t>NODE_S1991_92_0087</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25096,6 +25638,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -25129,6 +25679,8 @@
           <t>NODE_S1991_92_0087</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25138,6 +25690,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -25526,6 +26086,8 @@
         </is>
       </c>
     </row>
+    <row r="114"/>
+    <row r="115"/>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
@@ -25655,6 +26217,7 @@
         </is>
       </c>
     </row>
+    <row r="123"/>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>

--- a/data/S1991_92_FINAL.xlsx
+++ b/data/S1991_92_FINAL.xlsx
@@ -1344,6 +1344,11 @@
           <t>HC Dukla Trenčín</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F13" t="n">
         <v>38</v>
       </c>
@@ -21104,8 +21109,6 @@
           <t>NODE_S1991_92_0009</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21161,8 +21164,6 @@
           <t>NODE_S1991_92_0009</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21218,8 +21219,6 @@
           <t>NODE_S1991_92_0009</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21275,8 +21274,6 @@
           <t>NODE_S1991_92_0009</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21332,8 +21329,6 @@
           <t>NODE_S1991_92_0001</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21389,8 +21384,6 @@
           <t>NODE_S1991_92_0009</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21446,8 +21439,6 @@
           <t>NODE_S1991_92_0009</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21620,7 +21611,6 @@
           <t>NODE_S1991_92_0023</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21736,7 +21726,6 @@
           <t>NODE_S1991_92_0004</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>NODE_S1991_92_0026</t>
@@ -21849,8 +21838,6 @@
           <t>NODE_S1991_92_0004</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21906,8 +21893,6 @@
           <t>NODE_S1991_92_0004</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21963,8 +21948,6 @@
           <t>NODE_S1991_92_0004</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22203,7 +22186,6 @@
           <t>NODE_S1991_92_0034</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22259,8 +22241,6 @@
           <t>NODE_S1991_92_0030</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22311,8 +22291,6 @@
           <t>NODE_S1991_92_0030</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22598,7 +22576,6 @@
           <t>NODE_S1991_92_0043</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22654,7 +22631,6 @@
           <t>NODE_S1991_92_0043</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22705,8 +22681,6 @@
           <t>NODE_S1991_92_0036</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22762,8 +22736,6 @@
           <t>NODE_S1991_92_0036</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22819,8 +22791,6 @@
           <t>NODE_S1991_92_0036</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22876,8 +22846,6 @@
           <t>NODE_S1991_92_0036</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23148,8 +23116,6 @@
           <t>NODE_S1991_92_0049</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23200,8 +23166,6 @@
           <t>NODE_S1991_92_0050</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23252,8 +23216,6 @@
           <t>NODE_S1991_92_0051</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23304,8 +23266,6 @@
           <t>NODE_S1991_92_0048</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23520,8 +23480,6 @@
           <t>NODE_S1991_92_0058</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23572,8 +23530,6 @@
           <t>NODE_S1991_92_0058</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24121,8 +24077,6 @@
           <t>NODE_S1991_92_0069</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24173,8 +24127,6 @@
           <t>NODE_S1991_92_0069</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24371,7 +24323,6 @@
           <t>NODE_S1991_92_0086</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24689,8 +24640,6 @@
           <t>NODE_S1991_92_0079</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24971,8 +24920,6 @@
           <t>NODE_S1991_92_0087</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25023,8 +24970,6 @@
           <t>NODE_S1991_92_0087</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25075,8 +25020,6 @@
           <t>NODE_S1991_92_0087</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25127,8 +25070,6 @@
           <t>NODE_S1991_92_0087</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25315,8 +25256,6 @@
           <t>NODE_S1991_92_0087</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25372,8 +25311,6 @@
           <t>NODE_S1991_92_0087</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25424,8 +25361,6 @@
           <t>NODE_S1991_92_0087</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25570,8 +25505,6 @@
           <t>NODE_S1991_92_0087</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25627,8 +25560,6 @@
           <t>NODE_S1991_92_0087</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25679,8 +25610,6 @@
           <t>NODE_S1991_92_0087</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26086,8 +26015,6 @@
         </is>
       </c>
     </row>
-    <row r="114"/>
-    <row r="115"/>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
@@ -26217,7 +26144,6 @@
         </is>
       </c>
     </row>
-    <row r="123"/>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
@@ -51900,7 +51826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52140,6 +52066,18 @@
       <c r="B20" t="inlineStr">
         <is>
           <t>II.SNHL západ: chybí výsledek Levice – Topoľčany a PDF hlásí chybu ve skóre; II.SNHL o umístění – střed: chybějí dvě závěrečná kola.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dukla Trenčín</t>
         </is>
       </c>
     </row>

--- a/data/S1991_92_FINAL.xlsx
+++ b/data/S1991_92_FINAL.xlsx
@@ -26015,6 +26015,8 @@
         </is>
       </c>
     </row>
+    <row r="114"/>
+    <row r="115"/>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
@@ -26144,6 +26146,7 @@
         </is>
       </c>
     </row>
+    <row r="123"/>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
